--- a/resources/templates/standard/J1100-11.xlsx
+++ b/resources/templates/standard/J1100-11.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="52">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>MDT 구성원 적격성 관리 기준</t>
   </si>
@@ -698,13 +701,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -737,22 +742,22 @@
       <c r="AI1" s="2"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL1" s="3"/>
       <c r="AM1" s="3"/>
       <c r="AN1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
       <c r="AQ1" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR1" s="3"/>
       <c r="AS1" s="3"/>
       <c r="AT1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU1" s="3"/>
       <c r="AV1" s="3"/>
@@ -795,7 +800,7 @@
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL2" s="4"/>
       <c r="AM2" s="4"/>
@@ -897,22 +902,22 @@
       <c r="AI4" s="2"/>
       <c r="AJ4" s="2"/>
       <c r="AK4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
       <c r="AN4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO4" s="5"/>
       <c r="AP4" s="5"/>
       <c r="AQ4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR4" s="5"/>
       <c r="AS4" s="5"/>
       <c r="AT4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU4" s="5"/>
       <c r="AV4" s="5"/>
@@ -969,7 +974,7 @@
     </row>
     <row r="6" ht="20.15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -983,7 +988,7 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -997,7 +1002,7 @@
       <c r="W6" s="9"/>
       <c r="X6" s="9"/>
       <c r="Y6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
@@ -1011,13 +1016,13 @@
       <c r="AI6" s="9"/>
       <c r="AJ6" s="9"/>
       <c r="AK6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP6" s="10"/>
       <c r="AQ6" s="10"/>
@@ -1079,7 +1084,7 @@
     </row>
     <row r="8" ht="20.15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -1087,7 +1092,7 @@
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
@@ -1095,7 +1100,7 @@
       <c r="K8" s="12"/>
       <c r="L8" s="12"/>
       <c r="M8" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
@@ -1135,7 +1140,7 @@
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1143,7 +1148,7 @@
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
       <c r="G9" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -1151,7 +1156,7 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N9" s="14"/>
       <c r="O9" s="14"/>
@@ -1197,7 +1202,7 @@
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
       <c r="G10" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -1205,7 +1210,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N10" s="14"/>
       <c r="O10" s="14"/>
@@ -1257,7 +1262,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
@@ -1309,7 +1314,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N12" s="16"/>
       <c r="O12" s="16"/>
@@ -1399,7 +1404,7 @@
     </row>
     <row r="14" ht="20.15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -1407,7 +1412,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
@@ -1509,7 +1514,7 @@
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -1611,7 +1616,7 @@
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -1757,7 +1762,7 @@
     </row>
     <row r="21" ht="20.15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -1914,7 +1919,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -1947,22 +1952,22 @@
       <c r="AI24" s="2"/>
       <c r="AJ24" s="2"/>
       <c r="AK24" s="9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL24" s="9"/>
       <c r="AM24" s="9"/>
       <c r="AN24" s="9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO24" s="9"/>
       <c r="AP24" s="9"/>
       <c r="AQ24" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR24" s="9"/>
       <c r="AS24" s="9"/>
       <c r="AT24" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU24" s="9"/>
       <c r="AV24" s="9"/>
@@ -2005,7 +2010,7 @@
       <c r="AI25" s="2"/>
       <c r="AJ25" s="2"/>
       <c r="AK25" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL25" s="4"/>
       <c r="AM25" s="4"/>
@@ -2107,22 +2112,22 @@
       <c r="AI27" s="2"/>
       <c r="AJ27" s="2"/>
       <c r="AK27" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
       <c r="AN27" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO27" s="5"/>
       <c r="AP27" s="5"/>
       <c r="AQ27" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR27" s="5"/>
       <c r="AS27" s="5"/>
       <c r="AT27" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU27" s="5"/>
       <c r="AV27" s="5"/>
@@ -2179,7 +2184,7 @@
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -2197,7 +2202,7 @@
       <c r="O29" s="9"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
@@ -2215,7 +2220,7 @@
       <c r="AE29" s="9"/>
       <c r="AF29" s="9"/>
       <c r="AG29" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH29" s="3"/>
       <c r="AI29" s="3"/>
@@ -2235,14 +2240,14 @@
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
@@ -2276,7 +2281,7 @@
       <c r="AJ30" s="12"/>
       <c r="AK30" s="12"/>
       <c r="AL30" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AM30" s="12"/>
       <c r="AN30" s="12"/>
@@ -2291,14 +2296,14 @@
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
       <c r="D31" s="20"/>
       <c r="E31" s="20"/>
       <c r="F31" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15"/>
@@ -2345,14 +2350,14 @@
     </row>
     <row r="32" ht="20.15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
       <c r="D32" s="21"/>
       <c r="E32" s="21"/>
       <c r="F32" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G32" s="15"/>
       <c r="H32" s="15"/>
@@ -2404,7 +2409,7 @@
       <c r="D33" s="21"/>
       <c r="E33" s="21"/>
       <c r="F33" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15"/>
@@ -2456,7 +2461,7 @@
       <c r="D34" s="21"/>
       <c r="E34" s="21"/>
       <c r="F34" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G34" s="15"/>
       <c r="H34" s="15"/>
@@ -2503,14 +2508,14 @@
     </row>
     <row r="35" ht="20.15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="20"/>
       <c r="D35" s="20"/>
       <c r="E35" s="20"/>
       <c r="F35" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G35" s="15"/>
       <c r="H35" s="15"/>
@@ -2562,7 +2567,7 @@
       <c r="D36" s="20"/>
       <c r="E36" s="20"/>
       <c r="F36" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
@@ -2614,7 +2619,7 @@
       <c r="D37" s="20"/>
       <c r="E37" s="20"/>
       <c r="F37" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
@@ -2666,7 +2671,7 @@
       <c r="D38" s="20"/>
       <c r="E38" s="20"/>
       <c r="F38" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G38" s="15"/>
       <c r="H38" s="15"/>
@@ -2718,7 +2723,7 @@
       <c r="D39" s="20"/>
       <c r="E39" s="20"/>
       <c r="F39" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
@@ -2765,14 +2770,14 @@
     </row>
     <row r="40" ht="20.15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
       <c r="D40" s="20"/>
       <c r="E40" s="20"/>
       <c r="F40" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
@@ -2824,7 +2829,7 @@
       <c r="D41" s="20"/>
       <c r="E41" s="20"/>
       <c r="F41" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G41" s="15"/>
       <c r="H41" s="15"/>
@@ -2876,7 +2881,7 @@
       <c r="D42" s="20"/>
       <c r="E42" s="20"/>
       <c r="F42" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
@@ -2928,7 +2933,7 @@
       <c r="D43" s="20"/>
       <c r="E43" s="20"/>
       <c r="F43" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G43" s="15"/>
       <c r="H43" s="15"/>
@@ -2975,7 +2980,7 @@
     </row>
     <row r="44" ht="18" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A44" s="22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
